--- a/Data-Week1/Ex4B_GTrends.xlsx
+++ b/Data-Week1/Ex4B_GTrends.xlsx
@@ -8,16 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c56c2cc58af3f605/Documents/DataAnalyticsFolder/Data-Week1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="14_{390D8EBF-C715-4840-A404-742D3650FB76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:8_{1261330B-0378-41F4-A967-8EF5A3019974}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="25780" windowHeight="20970" xr2:uid="{F6DCEF2C-61BC-40D1-A867-BD577A37BE9D}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="25780" windowHeight="20970" activeTab="1" xr2:uid="{F6DCEF2C-61BC-40D1-A867-BD577A37BE9D}"/>
   </bookViews>
   <sheets>
-    <sheet name="geoMap" sheetId="1" r:id="rId1"/>
+    <sheet name="By search name" sheetId="2" r:id="rId1"/>
+    <sheet name="By state" sheetId="3" r:id="rId2"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">geoMap!$B$1:$E$52</definedName>
-  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
@@ -39,20 +37,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="56" uniqueCount="56">
+<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="112" uniqueCount="57">
   <si>
     <t>Region</t>
   </si>
   <si>
-    <t>Milkshake: (2/1/24 - 2/28/25)</t>
-  </si>
-  <si>
-    <t>Hamburger: (2/1/24 - 2/28/25)</t>
-  </si>
-  <si>
-    <t>Breakup: (2/1/24 - 2/28/25)</t>
-  </si>
-  <si>
     <t>South Carolina</t>
   </si>
   <si>
@@ -207,6 +196,18 @@
   </si>
   <si>
     <t>RegionID</t>
+  </si>
+  <si>
+    <t>"Data Range"</t>
+  </si>
+  <si>
+    <t>Hamburger: ()</t>
+  </si>
+  <si>
+    <t>Milkshake: ()</t>
+  </si>
+  <si>
+    <t>Breakup: ()</t>
   </si>
 </sst>
 </file>
@@ -1077,42 +1078,47 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1138A74F-018C-4B71-B71C-1DB09540436C}">
-  <dimension ref="A1:G54"/>
+<worksheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65ADA86B-DF84-45F0-A442-D989C6363245}">
+  <dimension ref="A1:J52"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11.81640625" customWidth="1"/>
-    <col min="2" max="2" width="29.1796875" customWidth="1"/>
-    <col min="3" max="3" width="29.26953125" customWidth="1"/>
-    <col min="4" max="4" width="25.90625" customWidth="1"/>
-    <col min="5" max="5" width="22.54296875" customWidth="1"/>
+    <col min="2" max="2" width="18.54296875" customWidth="1"/>
+    <col min="3" max="3" width="13.453125" customWidth="1"/>
+    <col min="4" max="4" width="15.08984375" customWidth="1"/>
+    <col min="5" max="5" width="10.08984375" customWidth="1"/>
+    <col min="10" max="10" width="12" customWidth="1"/>
+    <col min="11" max="11" width="14.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>2</v>
+        <v>54</v>
       </c>
       <c r="D1" t="s">
-        <v>1</v>
+        <v>55</v>
       </c>
       <c r="E1" t="s">
-        <v>3</v>
+        <v>56</v>
       </c>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="J1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" s="3">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C2" s="1">
         <v>0.65</v>
@@ -1124,12 +1130,12 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" s="3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C3" s="1">
         <v>0.71</v>
@@ -1141,12 +1147,12 @@
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" s="3">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C4" s="1">
         <v>0.66</v>
@@ -1158,12 +1164,12 @@
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" s="3">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C5" s="1">
         <v>0.66</v>
@@ -1175,12 +1181,12 @@
         <v>0.13</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" s="3">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C6" s="1">
         <v>0.65</v>
@@ -1192,12 +1198,12 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" s="3">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C7" s="1">
         <v>0.67</v>
@@ -1209,12 +1215,12 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" s="3">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C8" s="1">
         <v>0.63</v>
@@ -1226,12 +1232,12 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9" s="3">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C9" s="1">
         <v>0.63</v>
@@ -1243,12 +1249,12 @@
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" s="3">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C10" s="1">
         <v>0.66</v>
@@ -1260,12 +1266,12 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11" s="3">
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C11" s="1">
         <v>0.65</v>
@@ -1277,12 +1283,12 @@
         <v>0.13</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12" s="3">
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C12" s="1">
         <v>0.63</v>
@@ -1294,12 +1300,12 @@
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13" s="3">
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C13" s="1">
         <v>0.73</v>
@@ -1311,12 +1317,12 @@
         <v>0.13</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14" s="3">
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C14" s="1">
         <v>0.66</v>
@@ -1328,12 +1334,12 @@
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15" s="3">
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C15" s="1">
         <v>0.63</v>
@@ -1345,12 +1351,12 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A16" s="3">
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C16" s="1">
         <v>0.63</v>
@@ -1367,7 +1373,7 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C17" s="1">
         <v>0.68</v>
@@ -1384,7 +1390,7 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C18" s="1">
         <v>0.67</v>
@@ -1401,7 +1407,7 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C19" s="1">
         <v>0.63</v>
@@ -1418,7 +1424,7 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C20" s="1">
         <v>0.67</v>
@@ -1435,7 +1441,7 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C21" s="1">
         <v>0.69</v>
@@ -1452,7 +1458,7 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C22" s="1">
         <v>0.62</v>
@@ -1469,7 +1475,7 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C23" s="1">
         <v>0.62</v>
@@ -1486,7 +1492,7 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C24" s="1">
         <v>0.65</v>
@@ -1503,7 +1509,7 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C25" s="1">
         <v>0.67</v>
@@ -1520,7 +1526,7 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C26" s="1">
         <v>0.69</v>
@@ -1537,7 +1543,7 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C27" s="1">
         <v>0.68</v>
@@ -1554,7 +1560,7 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C28" s="1">
         <v>0.75</v>
@@ -1571,7 +1577,7 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C29" s="1">
         <v>0.69</v>
@@ -1588,7 +1594,7 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C30" s="1">
         <v>0.66</v>
@@ -1605,7 +1611,7 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C31" s="1">
         <v>0.68</v>
@@ -1622,7 +1628,7 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C32" s="1">
         <v>0.6</v>
@@ -1639,7 +1645,7 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C33" s="1">
         <v>0.69</v>
@@ -1656,7 +1662,7 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C34" s="1">
         <v>0.62</v>
@@ -1673,7 +1679,7 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C35" s="1">
         <v>0.64</v>
@@ -1690,7 +1696,7 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C36" s="1">
         <v>0.69</v>
@@ -1707,7 +1713,7 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C37" s="1">
         <v>0.65</v>
@@ -1724,7 +1730,7 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C38" s="1">
         <v>0.69</v>
@@ -1741,7 +1747,7 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C39" s="1">
         <v>0.69</v>
@@ -1758,7 +1764,7 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C40" s="1">
         <v>0.61</v>
@@ -1775,7 +1781,7 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C41" s="1">
         <v>0.63</v>
@@ -1792,7 +1798,7 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C42" s="1">
         <v>0.67</v>
@@ -1809,7 +1815,7 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C43" s="1">
         <v>0.75</v>
@@ -1826,7 +1832,7 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C44" s="1">
         <v>0.66</v>
@@ -1843,7 +1849,7 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C45" s="1">
         <v>0.68</v>
@@ -1860,7 +1866,7 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C46" s="1">
         <v>0.63</v>
@@ -1877,7 +1883,7 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C47" s="1">
         <v>0.69</v>
@@ -1894,7 +1900,7 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C48" s="1">
         <v>0.63</v>
@@ -1911,7 +1917,7 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C49" s="1">
         <v>0.67</v>
@@ -1928,7 +1934,7 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C50" s="1">
         <v>0.64</v>
@@ -1945,7 +1951,7 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C51" s="1">
         <v>0.66</v>
@@ -1962,7 +1968,7 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C52" s="1">
         <v>0.7</v>
@@ -1974,18 +1980,649 @@
         <v>0.13</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A54">
-        <f>COUNTA(B2:B52)</f>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFE7686B-61C6-4F9B-BD4A-B0B007F5CC00}">
+  <dimension ref="A1:AZ4"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:52" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G1" t="s">
+        <v>38</v>
+      </c>
+      <c r="H1" t="s">
+        <v>19</v>
+      </c>
+      <c r="I1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J1" t="s">
         <v>51</v>
       </c>
+      <c r="K1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L1" t="s">
+        <v>9</v>
+      </c>
+      <c r="M1" t="s">
+        <v>50</v>
+      </c>
+      <c r="N1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" t="s">
+        <v>12</v>
+      </c>
+      <c r="P1" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>32</v>
+      </c>
+      <c r="R1" t="s">
+        <v>28</v>
+      </c>
+      <c r="S1" t="s">
+        <v>3</v>
+      </c>
+      <c r="T1" t="s">
+        <v>26</v>
+      </c>
+      <c r="U1" t="s">
+        <v>45</v>
+      </c>
+      <c r="V1" t="s">
+        <v>23</v>
+      </c>
+      <c r="W1" t="s">
+        <v>42</v>
+      </c>
+      <c r="X1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>20</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>48</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>21</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>22</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>39</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AJ1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AK1" t="s">
+        <v>11</v>
+      </c>
+      <c r="AL1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AM1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AN1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AO1" t="s">
+        <v>8</v>
+      </c>
+      <c r="AP1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AQ1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AR1" t="s">
+        <v>5</v>
+      </c>
+      <c r="AS1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AT1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AU1" t="s">
+        <v>47</v>
+      </c>
+      <c r="AV1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AW1" t="s">
+        <v>40</v>
+      </c>
+      <c r="AX1" t="s">
+        <v>14</v>
+      </c>
+      <c r="AY1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AZ1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2" spans="1:52" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B2" s="1">
+        <v>0.65</v>
+      </c>
+      <c r="C2" s="1">
+        <v>0.71</v>
+      </c>
+      <c r="D2" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="E2" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="F2" s="1">
+        <v>0.65</v>
+      </c>
+      <c r="G2" s="1">
+        <v>0.67</v>
+      </c>
+      <c r="H2" s="1">
+        <v>0.63</v>
+      </c>
+      <c r="I2" s="1">
+        <v>0.63</v>
+      </c>
+      <c r="J2" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="K2" s="1">
+        <v>0.65</v>
+      </c>
+      <c r="L2" s="1">
+        <v>0.63</v>
+      </c>
+      <c r="M2" s="1">
+        <v>0.73</v>
+      </c>
+      <c r="N2" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="O2" s="1">
+        <v>0.63</v>
+      </c>
+      <c r="P2" s="1">
+        <v>0.63</v>
+      </c>
+      <c r="Q2" s="1">
+        <v>0.68</v>
+      </c>
+      <c r="R2" s="1">
+        <v>0.67</v>
+      </c>
+      <c r="S2" s="1">
+        <v>0.63</v>
+      </c>
+      <c r="T2" s="1">
+        <v>0.67</v>
+      </c>
+      <c r="U2" s="1">
+        <v>0.69</v>
+      </c>
+      <c r="V2" s="1">
+        <v>0.62</v>
+      </c>
+      <c r="W2" s="1">
+        <v>0.62</v>
+      </c>
+      <c r="X2" s="1">
+        <v>0.65</v>
+      </c>
+      <c r="Y2" s="1">
+        <v>0.67</v>
+      </c>
+      <c r="Z2" s="1">
+        <v>0.69</v>
+      </c>
+      <c r="AA2" s="1">
+        <v>0.68</v>
+      </c>
+      <c r="AB2" s="1">
+        <v>0.75</v>
+      </c>
+      <c r="AC2" s="1">
+        <v>0.69</v>
+      </c>
+      <c r="AD2" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="AE2" s="1">
+        <v>0.68</v>
+      </c>
+      <c r="AF2" s="1">
+        <v>0.6</v>
+      </c>
+      <c r="AG2" s="1">
+        <v>0.69</v>
+      </c>
+      <c r="AH2" s="1">
+        <v>0.62</v>
+      </c>
+      <c r="AI2" s="1">
+        <v>0.64</v>
+      </c>
+      <c r="AJ2" s="1">
+        <v>0.69</v>
+      </c>
+      <c r="AK2" s="1">
+        <v>0.65</v>
+      </c>
+      <c r="AL2" s="1">
+        <v>0.69</v>
+      </c>
+      <c r="AM2" s="1">
+        <v>0.69</v>
+      </c>
+      <c r="AN2" s="1">
+        <v>0.61</v>
+      </c>
+      <c r="AO2" s="1">
+        <v>0.63</v>
+      </c>
+      <c r="AP2" s="1">
+        <v>0.67</v>
+      </c>
+      <c r="AQ2" s="1">
+        <v>0.75</v>
+      </c>
+      <c r="AR2" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="AS2" s="1">
+        <v>0.68</v>
+      </c>
+      <c r="AT2" s="1">
+        <v>0.63</v>
+      </c>
+      <c r="AU2" s="1">
+        <v>0.69</v>
+      </c>
+      <c r="AV2" s="1">
+        <v>0.63</v>
+      </c>
+      <c r="AW2" s="1">
+        <v>0.67</v>
+      </c>
+      <c r="AX2" s="1">
+        <v>0.64</v>
+      </c>
+      <c r="AY2" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="AZ2" s="1">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:52" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B3" s="1">
+        <v>0.23</v>
+      </c>
+      <c r="C3" s="1">
+        <v>0.15</v>
+      </c>
+      <c r="D3" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="E3" s="1">
+        <v>0.21</v>
+      </c>
+      <c r="F3" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="G3" s="1">
+        <v>0.18</v>
+      </c>
+      <c r="H3" s="1">
+        <v>0.22</v>
+      </c>
+      <c r="I3" s="1">
+        <v>0.23</v>
+      </c>
+      <c r="J3" s="1">
+        <v>0.17</v>
+      </c>
+      <c r="K3" s="1">
+        <v>0.22</v>
+      </c>
+      <c r="L3" s="1">
+        <v>0.23</v>
+      </c>
+      <c r="M3" s="1">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="N3" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="O3" s="1">
+        <v>0.22</v>
+      </c>
+      <c r="P3" s="1">
+        <v>0.23</v>
+      </c>
+      <c r="Q3" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="R3" s="1">
+        <v>0.19</v>
+      </c>
+      <c r="S3" s="1">
+        <v>0.24</v>
+      </c>
+      <c r="T3" s="1">
+        <v>0.21</v>
+      </c>
+      <c r="U3" s="1">
+        <v>0.18</v>
+      </c>
+      <c r="V3" s="1">
+        <v>0.23</v>
+      </c>
+      <c r="W3" s="1">
+        <v>0.21</v>
+      </c>
+      <c r="X3" s="1">
+        <v>0.21</v>
+      </c>
+      <c r="Y3" s="1">
+        <v>0.19</v>
+      </c>
+      <c r="Z3" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="AA3" s="1">
+        <v>0.19</v>
+      </c>
+      <c r="AB3" s="1">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="AC3" s="1">
+        <v>0.17</v>
+      </c>
+      <c r="AD3" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="AE3" s="1">
+        <v>0.19</v>
+      </c>
+      <c r="AF3" s="1">
+        <v>0.24</v>
+      </c>
+      <c r="AG3" s="1">
+        <v>0.17</v>
+      </c>
+      <c r="AH3" s="1">
+        <v>0.21</v>
+      </c>
+      <c r="AI3" s="1">
+        <v>0.24</v>
+      </c>
+      <c r="AJ3" s="1">
+        <v>0.19</v>
+      </c>
+      <c r="AK3" s="1">
+        <v>0.22</v>
+      </c>
+      <c r="AL3" s="1">
+        <v>0.19</v>
+      </c>
+      <c r="AM3" s="1">
+        <v>0.18</v>
+      </c>
+      <c r="AN3" s="1">
+        <v>0.24</v>
+      </c>
+      <c r="AO3" s="1">
+        <v>0.24</v>
+      </c>
+      <c r="AP3" s="1">
+        <v>0.22</v>
+      </c>
+      <c r="AQ3" s="1">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="AR3" s="1">
+        <v>0.22</v>
+      </c>
+      <c r="AS3" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="AT3" s="1">
+        <v>0.23</v>
+      </c>
+      <c r="AU3" s="1">
+        <v>0.17</v>
+      </c>
+      <c r="AV3" s="1">
+        <v>0.23</v>
+      </c>
+      <c r="AW3" s="1">
+        <v>0.18</v>
+      </c>
+      <c r="AX3" s="1">
+        <v>0.23</v>
+      </c>
+      <c r="AY3" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="AZ3" s="1">
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:52" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B4" s="1">
+        <v>0.12</v>
+      </c>
+      <c r="C4" s="1">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="D4" s="1">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="E4" s="1">
+        <v>0.13</v>
+      </c>
+      <c r="F4" s="1">
+        <v>0.15</v>
+      </c>
+      <c r="G4" s="1">
+        <v>0.15</v>
+      </c>
+      <c r="H4" s="1">
+        <v>0.15</v>
+      </c>
+      <c r="I4" s="1">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="J4" s="1">
+        <v>0.17</v>
+      </c>
+      <c r="K4" s="1">
+        <v>0.13</v>
+      </c>
+      <c r="L4" s="1">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="M4" s="1">
+        <v>0.13</v>
+      </c>
+      <c r="N4" s="1">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="O4" s="1">
+        <v>0.15</v>
+      </c>
+      <c r="P4" s="1">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="Q4" s="1">
+        <v>0.12</v>
+      </c>
+      <c r="R4" s="1">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="S4" s="1">
+        <v>0.13</v>
+      </c>
+      <c r="T4" s="1">
+        <v>0.12</v>
+      </c>
+      <c r="U4" s="1">
+        <v>0.13</v>
+      </c>
+      <c r="V4" s="1">
+        <v>0.15</v>
+      </c>
+      <c r="W4" s="1">
+        <v>0.17</v>
+      </c>
+      <c r="X4" s="1">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="Y4" s="1">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="Z4" s="1">
+        <v>0.11</v>
+      </c>
+      <c r="AA4" s="1">
+        <v>0.13</v>
+      </c>
+      <c r="AB4" s="1">
+        <v>0.11</v>
+      </c>
+      <c r="AC4" s="1">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="AD4" s="1">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="AE4" s="1">
+        <v>0.13</v>
+      </c>
+      <c r="AF4" s="1">
+        <v>0.16</v>
+      </c>
+      <c r="AG4" s="1">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="AH4" s="1">
+        <v>0.17</v>
+      </c>
+      <c r="AI4" s="1">
+        <v>0.12</v>
+      </c>
+      <c r="AJ4" s="1">
+        <v>0.12</v>
+      </c>
+      <c r="AK4" s="1">
+        <v>0.13</v>
+      </c>
+      <c r="AL4" s="1">
+        <v>0.12</v>
+      </c>
+      <c r="AM4" s="1">
+        <v>0.13</v>
+      </c>
+      <c r="AN4" s="1">
+        <v>0.15</v>
+      </c>
+      <c r="AO4" s="1">
+        <v>0.13</v>
+      </c>
+      <c r="AP4" s="1">
+        <v>0.11</v>
+      </c>
+      <c r="AQ4" s="1">
+        <v>0.11</v>
+      </c>
+      <c r="AR4" s="1">
+        <v>0.12</v>
+      </c>
+      <c r="AS4" s="1">
+        <v>0.12</v>
+      </c>
+      <c r="AT4" s="1">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="AU4" s="1">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="AV4" s="1">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="AW4" s="1">
+        <v>0.15</v>
+      </c>
+      <c r="AX4" s="1">
+        <v>0.13</v>
+      </c>
+      <c r="AY4" s="1">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="AZ4" s="1">
+        <v>0.13</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D52" xr:uid="{1138A74F-018C-4B71-B71C-1DB09540436C}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D52">
-      <sortCondition ref="A1:A52"/>
-    </sortState>
-  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>